--- a/02_DIA_inicio_2026_analisis_assets/rbd_9740_escuela-basica-republica-de-las-filipinas_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9740_escuela-basica-republica-de-las-filipinas_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E138424-3718-4E84-B6BB-137A19D09AE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{525F939C-1D1F-4143-A4C0-AE0949D83D35}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D0EFA6D-8117-45A8-A642-BBBBA54F7B40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF7CEDD9-8947-4D12-8CB0-C954123C2340}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74BC4B9-D0A4-4602-94C3-83F8A28FD79D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C20D1AB5-9CC5-4BF2-9606-00FFC431FAA0}"/>
 </file>